--- a/design/设计书.xlsx
+++ b/design/设计书.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\seki\AI\Langchain\SIS_Agent\design\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269B00AC-E809-4E29-9D02-900899A2775F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="整体架构" sheetId="3" r:id="rId1"/>
@@ -22,9 +28,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -51,9 +58,6 @@
     <t>4.深究父子检索无法召回的bug</t>
   </si>
   <si>
-    <t>5.RAG评估（如用RAGAS评估检索质量）</t>
-  </si>
-  <si>
     <t>6.强制打断对话</t>
   </si>
   <si>
@@ -67,9 +71,6 @@
   </si>
   <si>
     <t>10.提示词进一步优化</t>
-  </si>
-  <si>
-    <t>11.MCP</t>
   </si>
   <si>
     <t>12.美化UI</t>
@@ -89,18 +90,20 @@
   <si>
     <t>code_agent</t>
   </si>
+  <si>
+    <t>5.RAG评估（用RAGAS评估检索质量）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.通过MCP服务器连接jira等</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,345 +127,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -550,256 +238,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -830,73 +276,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -910,9 +313,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>100292</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="矩形: 圆角 1"/>
+        <xdr:cNvPr id="2" name="矩形: 圆角 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -968,9 +377,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>18116</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="直接连接符 5"/>
+        <xdr:cNvPr id="6" name="直接连接符 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="55" idx="3"/>
           <a:endCxn id="2" idx="1"/>
@@ -1015,9 +430,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>69476</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="矩形: 圆角 7"/>
+        <xdr:cNvPr id="8" name="矩形: 圆角 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1058,7 +479,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
             <a:t>：文档翻译</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1077,9 +497,15 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>69477</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="连接符: 肘形 8"/>
+        <xdr:cNvPr id="9" name="连接符: 肘形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="0"/>
           <a:endCxn id="2" idx="2"/>
@@ -1119,20 +545,26 @@
       <xdr:rowOff>1681</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>324971</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>515471</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>1681</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="矩形 11"/>
+        <xdr:cNvPr id="12" name="矩形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="95250" y="3201670"/>
-          <a:ext cx="9982835" cy="5334000"/>
+          <a:off x="95250" y="3228975"/>
+          <a:ext cx="10707221" cy="5378824"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1194,9 +626,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="文本框 12"/>
+        <xdr:cNvPr id="13" name="文本框 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1250,25 +688,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>419735</xdr:colOff>
+      <xdr:colOff>139588</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>55880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>181610</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>503406</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>133573</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="矩形: 圆角 13"/>
+        <xdr:cNvPr id="14" name="矩形: 圆角 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5296535" y="5034280"/>
-          <a:ext cx="1590675" cy="788670"/>
+          <a:off x="4980529" y="5076115"/>
+          <a:ext cx="1574053" cy="794870"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -1310,7 +754,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
             <a:t>（基于火山引擎搜索工具）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1319,19 +762,25 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>320357</xdr:colOff>
+      <xdr:colOff>324596</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>98742</xdr:rowOff>
+      <xdr:rowOff>103467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>604202</xdr:colOff>
+      <xdr:colOff>324672</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>55562</xdr:rowOff>
+      <xdr:rowOff>55880</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="连接符: 肘形 14"/>
+        <xdr:cNvPr id="15" name="连接符: 肘形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="14" idx="0"/>
           <a:endCxn id="2" idx="2"/>
@@ -1339,12 +788,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipV="1">
-          <a:off x="4902835" y="3846195"/>
-          <a:ext cx="2090420" cy="283845"/>
+          <a:off x="4718722" y="4024106"/>
+          <a:ext cx="2103942" cy="76"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 50015"/>
+            <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -1378,9 +827,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>148590</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="矩形: 圆角 17"/>
+        <xdr:cNvPr id="18" name="矩形: 圆角 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1429,7 +884,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
             <a:t>本地知识库检索</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1437,26 +891,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>588010</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>221391</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>70485</xdr:rowOff>
+      <xdr:rowOff>41723</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>346710</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>585209</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>138653</xdr:rowOff>
+      <xdr:rowOff>116241</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="矩形: 圆角 19"/>
+        <xdr:cNvPr id="20" name="矩形: 圆角 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7903210" y="5048885"/>
-          <a:ext cx="1587500" cy="779145"/>
+          <a:off x="6877685" y="5061958"/>
+          <a:ext cx="1574053" cy="791695"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -1491,7 +951,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
             <a:t>：交接工具</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1500,19 +959,25 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>320357</xdr:colOff>
+      <xdr:colOff>324596</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>98742</xdr:rowOff>
+      <xdr:rowOff>103467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>162877</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>400125</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>70167</xdr:rowOff>
+      <xdr:rowOff>44898</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="连接符: 肘形 20"/>
+        <xdr:cNvPr id="21" name="连接符: 肘形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="20" idx="0"/>
           <a:endCxn id="2" idx="2"/>
@@ -1520,8 +985,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipV="1">
-          <a:off x="6198870" y="2550160"/>
-          <a:ext cx="2105025" cy="2890520"/>
+          <a:off x="5669616" y="3073212"/>
+          <a:ext cx="2092960" cy="1890882"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -1559,9 +1024,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>108324</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="矩形: 圆角 44"/>
+        <xdr:cNvPr id="45" name="矩形: 圆角 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1617,9 +1088,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>39406</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="矩形: 圆角 45"/>
+        <xdr:cNvPr id="46" name="矩形: 圆角 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1675,9 +1152,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>112060</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="47" name="连接符: 肘形 46"/>
+        <xdr:cNvPr id="47" name="连接符: 肘形 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="0"/>
           <a:endCxn id="46" idx="2"/>
@@ -1724,9 +1207,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>104216</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="连接符: 肘形 51"/>
+        <xdr:cNvPr id="52" name="连接符: 肘形 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="45" idx="0"/>
           <a:endCxn id="46" idx="2"/>
@@ -1773,9 +1262,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>106642</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="矩形: 圆角 54"/>
+        <xdr:cNvPr id="55" name="矩形: 圆角 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1883,9 +1378,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>15035</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="58" name="直接连接符 57"/>
+        <xdr:cNvPr id="58" name="直接连接符 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="59" idx="1"/>
           <a:endCxn id="45" idx="3"/>
@@ -1930,9 +1431,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>84230</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="59" name="矩形: 圆角 58"/>
+        <xdr:cNvPr id="59" name="矩形: 圆角 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2040,9 +1547,15 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>83502</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="67" name="连接符: 肘形 66"/>
+        <xdr:cNvPr id="67" name="连接符: 肘形 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="18" idx="0"/>
           <a:endCxn id="2" idx="2"/>
@@ -2089,9 +1602,15 @@
       <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="77" name="矩形 76"/>
+        <xdr:cNvPr id="77" name="矩形 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2159,9 +1678,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>74519</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="81" name="矩形: 圆角 80"/>
+        <xdr:cNvPr id="81" name="矩形: 圆角 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2210,7 +1735,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
             <a:t>命令</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2229,9 +1753,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>15500</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="82" name="矩形: 圆角 81"/>
+        <xdr:cNvPr id="82" name="矩形: 圆角 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2272,7 +1802,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
             <a:t>：读文件</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2291,9 +1820,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>2540</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="矩形: 圆角 81"/>
+        <xdr:cNvPr id="3" name="矩形: 圆角 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2432,7 +1967,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
             <a:t>：写文件</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2451,9 +1985,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>31115</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="矩形: 圆角 19"/>
+        <xdr:cNvPr id="5" name="矩形: 圆角 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2592,7 +2132,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
             <a:t>：交接工具</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2611,9 +2150,15 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>8890</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="连接符: 肘形 20"/>
+        <xdr:cNvPr id="7" name="连接符: 肘形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="81" idx="0"/>
           <a:endCxn id="45" idx="2"/>
@@ -2660,9 +2205,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>145097</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="连接符: 肘形 20"/>
+        <xdr:cNvPr id="10" name="连接符: 肘形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="82" idx="0"/>
           <a:endCxn id="45" idx="2"/>
@@ -2709,9 +2260,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>132080</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="连接符: 肘形 20"/>
+        <xdr:cNvPr id="11" name="连接符: 肘形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="3" idx="0"/>
           <a:endCxn id="45" idx="2"/>
@@ -2758,9 +2315,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>140970</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="连接符: 肘形 20"/>
+        <xdr:cNvPr id="16" name="连接符: 肘形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="5" idx="0"/>
           <a:endCxn id="45" idx="2"/>
@@ -2794,11 +2357,134 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>324597</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>103467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>550116</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>64061</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="连接符: 肘形 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2039A3DE-A2F1-4C71-A5A5-C4E1C343E729}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="36" idx="0"/>
+          <a:endCxn id="2" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipV="1">
+          <a:off x="6642707" y="2100122"/>
+          <a:ext cx="2112123" cy="3856225"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>369794</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>67236</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>118969</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>132229</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="矩形: 圆角 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED49BCE9-7D56-40A6-9CCD-9C1D500AEF3B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8841441" y="5087471"/>
+          <a:ext cx="1564528" cy="782170"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
+            <a:t>可扩展</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
+            <a:t>skills</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -2812,9 +2498,15 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="圆角矩形 1"/>
+        <xdr:cNvPr id="2" name="圆角矩形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2987,9 +2679,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="圆角矩形 2"/>
+        <xdr:cNvPr id="3" name="圆角矩形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3162,9 +2860,15 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="圆角矩形 3"/>
+        <xdr:cNvPr id="4" name="圆角矩形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3337,9 +3041,15 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="圆角矩形 4"/>
+        <xdr:cNvPr id="5" name="圆角矩形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3512,9 +3222,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="圆角矩形 5"/>
+        <xdr:cNvPr id="6" name="圆角矩形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3687,9 +3403,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="圆角矩形 6"/>
+        <xdr:cNvPr id="7" name="圆角矩形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3862,9 +3584,15 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="圆角矩形 7"/>
+        <xdr:cNvPr id="8" name="圆角矩形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4037,9 +3765,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="曲线连接符 8"/>
+        <xdr:cNvPr id="9" name="曲线连接符 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="1"/>
           <a:endCxn id="3" idx="0"/>
@@ -4087,9 +3821,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="曲线连接符 9"/>
+        <xdr:cNvPr id="10" name="曲线连接符 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="3" idx="1"/>
           <a:endCxn id="4" idx="0"/>
@@ -4137,9 +3877,15 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="曲线连接符 10"/>
+        <xdr:cNvPr id="11" name="曲线连接符 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="4" idx="3"/>
           <a:endCxn id="5" idx="0"/>
@@ -4187,9 +3933,15 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="圆角矩形 11"/>
+        <xdr:cNvPr id="12" name="圆角矩形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4362,9 +4114,15 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="圆角矩形 12"/>
+        <xdr:cNvPr id="13" name="圆角矩形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4537,9 +4295,15 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="曲线连接符 13"/>
+        <xdr:cNvPr id="14" name="曲线连接符 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="5" idx="2"/>
           <a:endCxn id="4" idx="2"/>
@@ -4589,9 +4353,15 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="曲线连接符 14"/>
+        <xdr:cNvPr id="15" name="曲线连接符 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="4" idx="1"/>
           <a:endCxn id="12" idx="1"/>
@@ -4641,9 +4411,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="曲线连接符 15"/>
+        <xdr:cNvPr id="16" name="曲线连接符 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="5" idx="3"/>
           <a:endCxn id="6" idx="1"/>
@@ -4693,9 +4469,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="圆角矩形 16"/>
+        <xdr:cNvPr id="17" name="圆角矩形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4868,9 +4650,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="18" name="曲线连接符 17"/>
+        <xdr:cNvPr id="18" name="曲线连接符 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="3"/>
           <a:endCxn id="6" idx="0"/>
@@ -4918,9 +4706,15 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="文本框 18"/>
+        <xdr:cNvPr id="19" name="文本框 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4967,7 +4761,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>route_initial</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4986,9 +4779,15 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="文本框 19"/>
+        <xdr:cNvPr id="20" name="文本框 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5133,7 +4932,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>route_initial</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5152,9 +4950,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="曲线连接符 20"/>
+        <xdr:cNvPr id="21" name="曲线连接符 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="12" idx="3"/>
           <a:endCxn id="17" idx="1"/>
@@ -5204,9 +5008,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="曲线连接符 21"/>
+        <xdr:cNvPr id="22" name="曲线连接符 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="13" idx="1"/>
           <a:endCxn id="17" idx="3"/>
@@ -5256,9 +5066,15 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="曲线连接符 22"/>
+        <xdr:cNvPr id="23" name="曲线连接符 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="2"/>
           <a:endCxn id="7" idx="0"/>
@@ -5308,9 +5124,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="24" name="曲线连接符 23"/>
+        <xdr:cNvPr id="24" name="曲线连接符 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="1"/>
           <a:endCxn id="8" idx="0"/>
@@ -5361,9 +5183,15 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="25" name="曲线连接符 24"/>
+        <xdr:cNvPr id="25" name="曲线连接符 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="1"/>
           <a:endCxn id="3" idx="3"/>
@@ -5413,9 +5241,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="26" name="曲线连接符 25"/>
+        <xdr:cNvPr id="26" name="曲线连接符 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="3"/>
           <a:endCxn id="7" idx="2"/>
@@ -5466,9 +5300,15 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="27" name="曲线连接符 26"/>
+        <xdr:cNvPr id="27" name="曲线连接符 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="3"/>
           <a:endCxn id="13" idx="3"/>
@@ -5518,9 +5358,15 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="文本框 27"/>
+        <xdr:cNvPr id="28" name="文本框 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5663,7 +5509,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>transfer_to_code_agent</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5682,9 +5527,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="文本框 28"/>
+        <xdr:cNvPr id="29" name="文本框 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5827,7 +5678,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>transfer_to_main_agent</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5837,7 +5687,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -5851,9 +5701,15 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="圆角矩形 1"/>
+        <xdr:cNvPr id="2" name="圆角矩形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5909,7 +5765,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>本地文档</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5928,9 +5783,15 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="圆角矩形 2"/>
+        <xdr:cNvPr id="3" name="圆角矩形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6084,7 +5945,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>用户</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6103,9 +5963,15 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="圆角矩形 3"/>
+        <xdr:cNvPr id="4" name="圆角矩形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6278,9 +6144,15 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="圆角矩形 4"/>
+        <xdr:cNvPr id="5" name="圆角矩形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6434,7 +6306,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -6442,7 +6313,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（qwen3.5-plus）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6461,9 +6331,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>95885</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="圆角矩形 5"/>
+        <xdr:cNvPr id="6" name="圆角矩形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6617,7 +6493,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>父文档</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6636,9 +6511,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="圆角矩形 6"/>
+        <xdr:cNvPr id="7" name="圆角矩形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6792,7 +6673,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>向量库</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -6808,7 +6688,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6827,9 +6706,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>62865</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="圆角矩形 7"/>
+        <xdr:cNvPr id="8" name="圆角矩形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6987,7 +6872,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -6995,7 +6879,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（qwen3.5-flash）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7014,9 +6897,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="圆角矩形 8"/>
+        <xdr:cNvPr id="9" name="圆角矩形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7174,7 +7063,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -7182,7 +7070,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（text-embedding-v4）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7201,9 +7088,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="直接连接符 9"/>
+        <xdr:cNvPr id="10" name="直接连接符 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="3" idx="2"/>
           <a:endCxn id="4" idx="0"/>
@@ -7252,9 +7145,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="直接连接符 10"/>
+        <xdr:cNvPr id="11" name="直接连接符 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="4" idx="3"/>
           <a:endCxn id="5" idx="1"/>
@@ -7303,9 +7202,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="肘形连接符 12"/>
+        <xdr:cNvPr id="13" name="肘形连接符 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="3"/>
           <a:endCxn id="9" idx="0"/>
@@ -7353,9 +7258,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="圆角矩形 16"/>
+        <xdr:cNvPr id="17" name="圆角矩形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7509,7 +7420,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>rag LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -7517,7 +7427,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（qwen-plus）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7536,9 +7445,15 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="18" name="直接连接符 17"/>
+        <xdr:cNvPr id="18" name="直接连接符 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="4" idx="2"/>
           <a:endCxn id="17" idx="0"/>
@@ -7586,9 +7501,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="直接连接符 18"/>
+        <xdr:cNvPr id="19" name="直接连接符 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="20" idx="3"/>
           <a:endCxn id="4" idx="1"/>
@@ -7637,9 +7558,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="圆角矩形 19"/>
+        <xdr:cNvPr id="20" name="圆角矩形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7793,7 +7720,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>融合检索器</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7812,9 +7738,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="肘形连接符 20"/>
+        <xdr:cNvPr id="21" name="肘形连接符 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="20" idx="1"/>
           <a:endCxn id="7" idx="3"/>
@@ -7864,9 +7796,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="直接连接符 21"/>
+        <xdr:cNvPr id="22" name="直接连接符 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="1"/>
           <a:endCxn id="6" idx="3"/>
@@ -7914,9 +7852,15 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="肘形连接符 22"/>
+        <xdr:cNvPr id="23" name="肘形连接符 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="20" idx="1"/>
           <a:endCxn id="6" idx="0"/>
@@ -7964,9 +7908,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="文本框 23"/>
+        <xdr:cNvPr id="24" name="文本框 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8017,7 +7967,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>检索</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8036,9 +7985,15 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="文本框 24"/>
+        <xdr:cNvPr id="25" name="文本框 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8187,7 +8142,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>子检索</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8206,9 +8160,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="文本框 25"/>
+        <xdr:cNvPr id="26" name="文本框 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8357,7 +8317,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>父检索</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8376,9 +8335,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="文本框 26"/>
+        <xdr:cNvPr id="27" name="文本框 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8527,7 +8492,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>用户输入</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8546,9 +8510,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>178435</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="文本框 27"/>
+        <xdr:cNvPr id="28" name="文本框 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8703,7 +8673,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>工具</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8722,9 +8691,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="文本框 28"/>
+        <xdr:cNvPr id="29" name="文本框 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8871,7 +8846,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>调用工具，检索本地向量库</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8890,9 +8864,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>100965</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="30" name="肘形连接符 29"/>
+        <xdr:cNvPr id="30" name="肘形连接符 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="2"/>
           <a:endCxn id="31" idx="1"/>
@@ -8940,9 +8920,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="圆角矩形 30"/>
+        <xdr:cNvPr id="31" name="圆角矩形 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9100,7 +9086,6 @@
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
             <a:t>LLM</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -9108,7 +9093,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>（qwen3-rerank）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -9127,9 +9111,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="文本框 31"/>
+        <xdr:cNvPr id="32" name="文本框 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9278,7 +9268,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>检索结果重排序</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -9297,9 +9286,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="肘形连接符 32"/>
+        <xdr:cNvPr id="33" name="肘形连接符 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="31" idx="3"/>
           <a:endCxn id="17" idx="1"/>
@@ -9347,9 +9342,15 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>126365</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="文本框 33"/>
+        <xdr:cNvPr id="34" name="文本框 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9519,9 +9520,15 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="文本框 34"/>
+        <xdr:cNvPr id="35" name="文本框 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9691,9 +9698,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="文本框 35"/>
+        <xdr:cNvPr id="36" name="文本框 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9842,7 +9855,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
             <a:t>输出答案</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -9861,9 +9873,15 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="直接连接符 36"/>
+        <xdr:cNvPr id="37" name="直接连接符 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="0"/>
           <a:endCxn id="9" idx="2"/>
@@ -9912,9 +9930,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="肘形连接符 37"/>
+        <xdr:cNvPr id="38" name="肘形连接符 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="1"/>
           <a:endCxn id="6" idx="1"/>
@@ -9964,9 +9988,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>43180</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="文本框 38"/>
+        <xdr:cNvPr id="39" name="文本框 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10136,9 +10166,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>62230</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="文本框 39"/>
+        <xdr:cNvPr id="40" name="文本框 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10291,7 +10327,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
@@ -10305,9 +10341,15 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>30816</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="矩形: 圆角 2"/>
+        <xdr:cNvPr id="3" name="矩形: 圆角 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10367,9 +10409,15 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>146610</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="矩形: 圆角 3"/>
+        <xdr:cNvPr id="4" name="矩形: 圆角 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10442,7 +10490,6 @@
             <a:rPr lang="zh-CN" altLang="en-US" sz="900" baseline="0"/>
             <a:t>（单线程）</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="900" baseline="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -10695,29 +10742,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C54:G69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.72727272727273" style="10"/>
+    <col min="1" max="16384" width="8.7265625" style="10"/>
   </cols>
   <sheetData>
-    <row r="54" spans="3:7">
+    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C54" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:7">
+    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D55" s="11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="3:7">
+    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D56" s="10" t="s">
         <v>2</v>
       </c>
@@ -10725,95 +10772,93 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="3:7">
+    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D57" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:7">
+    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D58" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:7">
-      <c r="D59" s="10" t="s">
+    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D59" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D60" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="3:7">
-      <c r="D60" s="10" t="s">
+    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D61" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="3:7">
-      <c r="D61" s="10" t="s">
+    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D62" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="3:7">
-      <c r="D62" s="12" t="s">
+    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D63" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="3:7">
-      <c r="D63" s="12" t="s">
+    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D64" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="3:7">
-      <c r="D64" s="12" t="s">
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D65" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D66" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="4:4">
-      <c r="D65" s="10" t="s">
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D67" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="4:4">
-      <c r="D66" s="10" t="s">
+    <row r="68" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D68" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="4:4">
-      <c r="D67" s="11" t="s">
+    <row r="69" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D69" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="4:4">
-      <c r="D68" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="4:4">
-      <c r="D69" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B8:T27"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="8" spans="2:20">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="9" ht="14.75"/>
-    <row r="10" spans="2:20">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -10829,103 +10874,103 @@
       <c r="S10" s="3"/>
       <c r="T10" s="4"/>
     </row>
-    <row r="11" spans="2:20">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
       <c r="H11" s="6"/>
       <c r="N11" s="5"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="2:20">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
       <c r="H12" s="6"/>
       <c r="N12" s="5"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="2:20">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" s="5"/>
       <c r="H13" s="6"/>
       <c r="N13" s="5"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="2:20">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
       <c r="H14" s="6"/>
       <c r="N14" s="5"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="2:20">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
       <c r="H15" s="6"/>
       <c r="N15" s="5"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="2:20">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" s="5"/>
       <c r="H16" s="6"/>
       <c r="N16" s="5"/>
       <c r="T16" s="6"/>
     </row>
-    <row r="17" spans="2:20">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="H17" s="6"/>
       <c r="N17" s="5"/>
       <c r="T17" s="6"/>
     </row>
-    <row r="18" spans="2:20">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="H18" s="6"/>
       <c r="N18" s="5"/>
       <c r="T18" s="6"/>
     </row>
-    <row r="19" spans="2:20">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="H19" s="6"/>
       <c r="N19" s="5"/>
       <c r="T19" s="6"/>
     </row>
-    <row r="20" spans="2:20">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="H20" s="6"/>
       <c r="N20" s="5"/>
       <c r="T20" s="6"/>
     </row>
-    <row r="21" spans="2:20">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="H21" s="6"/>
       <c r="N21" s="5"/>
       <c r="T21" s="6"/>
     </row>
-    <row r="22" spans="2:20">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="H22" s="6"/>
       <c r="N22" s="5"/>
       <c r="T22" s="6"/>
     </row>
-    <row r="23" spans="2:20">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="H23" s="6"/>
       <c r="N23" s="5"/>
       <c r="T23" s="6"/>
     </row>
-    <row r="24" spans="2:20">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="H24" s="6"/>
       <c r="N24" s="5"/>
       <c r="T24" s="6"/>
     </row>
-    <row r="25" spans="2:20">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="H25" s="6"/>
       <c r="N25" s="5"/>
       <c r="T25" s="6"/>
     </row>
-    <row r="26" spans="2:20">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
       <c r="H26" s="6"/>
       <c r="N26" s="5"/>
       <c r="T26" s="6"/>
     </row>
-    <row r="27" ht="14.75" spans="2:20">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" s="7"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -10942,43 +10987,40 @@
       <c r="T27" s="9"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>